--- a/Employee_Reports_wi48/Sampath Chamin Q0208.xlsx
+++ b/Employee_Reports_wi48/Sampath Chamin Q0208.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1656,9 +1656,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1670,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1719,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1768,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1817,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1854,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1891,11 +1903,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1928,11 +1940,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1977,11 +1989,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2014,11 +2026,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2051,11 +2063,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2217,7 +2229,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7943</v>
+        <v>7940</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2240,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2312,7 +2324,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2353,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2370,7 +2382,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2411,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2428,7 +2440,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2457,7 +2469,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2486,7 +2498,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2515,7 +2527,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2544,7 +2556,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2573,7 +2585,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2593,16 +2605,16 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2622,16 +2634,16 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2651,16 +2663,16 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2680,16 +2692,16 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2718,7 +2730,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2747,7 +2759,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2755,6 +2767,35 @@
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
